--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484205_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484205_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8053</v>
+        <v>5.7647</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4623</v>
+        <v>5.4217</v>
       </c>
       <c r="F2" t="n">
         <v>0.3431</v>
@@ -610,10 +610,10 @@
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3026</v>
+        <v>0.262</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0522</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U2" t="n">
         <v>0.3548</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4466</v>
+        <v>5.2245</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8362</v>
+        <v>4.3418</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.8827</v>
       </c>
       <c r="G3" t="n">
         <v>4.3139</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3482</v>
+        <v>-0.5703</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.3417</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5009</v>
+        <v>-0.2285</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4999</v>
+        <v>3.3181</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0854</v>
+        <v>2.0672</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4146</v>
+        <v>1.251</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1963</v>
+        <v>0.9049</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4288</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7675</v>
+        <v>1.4155</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6217</v>
+        <v>0.3251</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3929</v>
+        <v>0.1228</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2288</v>
+        <v>0.2023</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5745</v>
+        <v>0.5798</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0359</v>
+        <v>-0.6334</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5387</v>
+        <v>1.2132</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3037</v>
+        <v>-0.6687</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4404</v>
+        <v>-0.3631</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1367</v>
+        <v>-0.3055</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1487</v>
+        <v>2.553</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0066</v>
+        <v>1.4381</v>
       </c>
       <c r="F5" t="n">
-        <v>1.142</v>
+        <v>1.115</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9049</v>
+        <v>3.1963</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5106000000000001</v>
+        <v>1.4288</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4155</v>
+        <v>1.7675</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3251</v>
+        <v>2.6217</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1228</v>
+        <v>1.3929</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2023</v>
+        <v>1.2288</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5798</v>
+        <v>0.5745</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6334</v>
+        <v>0.0359</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2132</v>
+        <v>0.5387</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8381</v>
+        <v>-0.6432</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4237</v>
+        <v>-0.2069</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4145</v>
+        <v>-0.4363</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.3557</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3134</v>
+        <v>-0.6867</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3583</v>
+        <v>0.3311</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4149</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3801</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1499</v>
+        <v>-0.5233</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2302</v>
+        <v>-0.2574</v>
       </c>
       <c r="V7" t="n">
         <v>0.2772</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9732</v>
+        <v>-0.6888</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9837</v>
+        <v>1.1047</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9569</v>
+        <v>-1.7935</v>
       </c>
       <c r="G8" t="n">
         <v>1.7951</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0493</v>
+        <v>-0.7649</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5364</v>
+        <v>-0.4153</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.513</v>
+        <v>-0.3496</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3283</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9646</v>
+        <v>-1.6668</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0178</v>
+        <v>-0.8561</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9469</v>
+        <v>-0.8107</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1063</v>
@@ -1156,13 +1156,13 @@
         <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2491</v>
+        <v>-0.9513</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6657</v>
+        <v>-0.5041</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5833</v>
+        <v>-0.4471</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7898</v>
+        <v>-5.0077</v>
       </c>
       <c r="E10" t="n">
         <v>-5.1228</v>
       </c>
       <c r="F10" t="n">
-        <v>0.333</v>
+        <v>0.1151</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3097</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6048</v>
+        <v>-0.8227</v>
       </c>
       <c r="T10" t="n">
         <v>-0.7262999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1215</v>
+        <v>-0.0964</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5545</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4165</v>
+        <v>-5.735</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.044</v>
+        <v>-3.2263</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3725</v>
+        <v>-2.5087</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6908</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3329</v>
+        <v>0.0144</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0689</v>
+        <v>-0.1134</v>
       </c>
       <c r="U11" t="n">
-        <v>0.264</v>
+        <v>0.1278</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1052</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.936100000000002</v>
+        <v>3.541100000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>3.876200000000001</v>
+        <v>4.4816</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9400999999999999</v>
+        <v>-0.9401000000000006</v>
       </c>
       <c r="G12" t="n">
         <v>10.7167</v>
@@ -1390,13 +1390,13 @@
         <v>9.766999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.5304</v>
+        <v>-4.925400000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8922</v>
+        <v>-3.2869</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6383</v>
+        <v>-1.6382</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2735</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8223</v>
+        <v>6.7641</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7157</v>
+        <v>6.1881</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1066</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0619</v>
+        <v>5.7047</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3307</v>
+        <v>1.8202</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2688</v>
+        <v>3.8845</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5197</v>
+        <v>7.3385</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6295</v>
+        <v>1.6999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8902</v>
+        <v>5.6386</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4579</v>
+        <v>-1.6338</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2988</v>
+        <v>0.1203</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1591</v>
+        <v>-1.754</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7056</v>
+        <v>0.6101</v>
       </c>
       <c r="T13" t="n">
-        <v>3.954</v>
+        <v>-0.1189</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8828</v>
+        <v>-0.3321</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>-0.0549</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0175</v>
+        <v>5.1817</v>
       </c>
       <c r="E14" t="n">
-        <v>5.278</v>
+        <v>3.8845</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7395</v>
+        <v>1.2972</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7047</v>
+        <v>0.0619</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8202</v>
+        <v>1.3307</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8845</v>
+        <v>-1.2688</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3385</v>
+        <v>2.5197</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6999</v>
+        <v>1.6295</v>
       </c>
       <c r="L14" t="n">
-        <v>5.6386</v>
+        <v>0.8902</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6338</v>
+        <v>-2.4579</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1203</v>
+        <v>-0.2988</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.754</v>
+        <v>-2.1591</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1365</v>
+        <v>2.065</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0289</v>
+        <v>1.1228</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8924</v>
+        <v>0.9422</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3321</v>
+        <v>1.8828</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0549</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2254</v>
+        <v>3.1285</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6165</v>
+        <v>3.0098</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6089</v>
+        <v>0.1186</v>
       </c>
       <c r="G15" t="n">
         <v>0.4133</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2456</v>
+        <v>1.1487</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0677</v>
+        <v>0.461</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1779</v>
+        <v>0.6877</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3869</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3874</v>
+        <v>2.1963</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8635</v>
+        <v>-0.0546</v>
       </c>
       <c r="F16" t="n">
         <v>2.251</v>
@@ -1702,10 +1702,10 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2696</v>
+        <v>0.5393</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9684</v>
+        <v>-0.1594</v>
       </c>
       <c r="U16" t="n">
         <v>0.6987</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1336</v>
+        <v>0.0959</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.254</v>
+        <v>-0.0518</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1204</v>
+        <v>0.1476</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5562</v>
@@ -1780,13 +1780,13 @@
         <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1634</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1059</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.2025</v>
+        <v>-3.923</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4314</v>
+        <v>-3.2674</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7712</v>
+        <v>-0.6556</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8171</v>
+        <v>-2.8561</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1981</v>
+        <v>1.2832</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.619</v>
+        <v>-4.1393</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3047</v>
+        <v>-1.2825</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3047</v>
+        <v>1.3725</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.6549</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5123</v>
+        <v>-1.5737</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8933</v>
+        <v>-0.0893</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.619</v>
+        <v>-1.4844</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1871</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2175</v>
+        <v>-0.0315</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1183</v>
+        <v>0.2186</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2735</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.6658</v>
+        <v>-4.0664</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8741</v>
+        <v>-2.4314</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7917</v>
+        <v>-1.635</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8561</v>
+        <v>-3.8171</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2832</v>
+        <v>-2.1981</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.1393</v>
+        <v>-1.619</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2825</v>
+        <v>-1.3047</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3725</v>
+        <v>-1.3047</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6549</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5737</v>
+        <v>-2.5123</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0893</v>
+        <v>-0.8933</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4844</v>
+        <v>-1.619</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5558</v>
+        <v>0.2353</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6382</v>
+        <v>0.2175</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0824</v>
+        <v>0.0178</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>1.2735</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.7286</v>
+        <v>-5.3358</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8941</v>
+        <v>-1.6918</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8346</v>
+        <v>-3.6439</v>
       </c>
       <c r="G20" t="n">
         <v>-3.9013</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.3935</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0851</v>
+        <v>0.1171</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0858</v>
+        <v>0.2764</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8279</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.6579</v>
+        <v>-6.9774</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.353</v>
+        <v>-4.6452</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3049</v>
+        <v>-2.3322</v>
       </c>
       <c r="G21" t="n">
         <v>-6.595</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3951</v>
+        <v>0.2855</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6382</v>
+        <v>0.0696</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2431</v>
+        <v>0.2159</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9358</v>
+        <v>-2.936099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.940100000000001</v>
+        <v>0.9402000000000017</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.876</v>
+        <v>-3.8762</v>
       </c>
       <c r="G22" t="n">
         <v>-10.7167</v>
@@ -2170,10 +2170,10 @@
         <v>10.7437</v>
       </c>
       <c r="S22" t="n">
-        <v>5.530499999999999</v>
+        <v>5.5306</v>
       </c>
       <c r="T22" t="n">
-        <v>1.638300000000001</v>
+        <v>1.6383</v>
       </c>
       <c r="U22" t="n">
         <v>3.8922</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484205_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484205_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1052</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-4.1006</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,11 +2039,16 @@
       <c r="X19" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2030,6 +2121,11 @@
       </c>
       <c r="X20" t="n">
         <v>-2.1052</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484205_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,7 @@
       <c r="X22" t="n">
         <v>-2.827</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
